--- a/tests/baselines/2026-08-29-stage-7/base.xlsx
+++ b/tests/baselines/2026-08-29-stage-7/base.xlsx
@@ -852,6 +852,7 @@
       </c>
       <c r="E2" s="4">
         <f>A53+7</f>
+        <v>46391</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>4</v>
@@ -862,6 +863,7 @@
     <row r="3" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <f>A2+7</f>
+        <v>46034</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -870,6 +872,7 @@
       <c r="D3" s="9"/>
       <c r="E3" s="4">
         <f>E2+7</f>
+        <v>46398</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>6</v>
@@ -880,6 +883,7 @@
     <row r="4" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <f>A3+7</f>
+        <v>46041</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>7</v>
@@ -890,6 +894,7 @@
       </c>
       <c r="E4" s="4">
         <f>E3+7</f>
+        <v>46405</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>9</v>
@@ -902,6 +907,7 @@
     <row r="5" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <f>A4+7</f>
+        <v>46048</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>11</v>
@@ -910,6 +916,7 @@
       <c r="D5" s="9"/>
       <c r="E5" s="4">
         <f>E4+7</f>
+        <v>46412</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>12</v>
@@ -920,6 +927,7 @@
     <row r="6" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <f>A5+7</f>
+        <v>46055</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>13</v>
@@ -928,6 +936,7 @@
       <c r="D6" s="9"/>
       <c r="E6" s="4">
         <f>E5+7</f>
+        <v>46419</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>14</v>
@@ -938,6 +947,7 @@
     <row r="7" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <f>A6+7</f>
+        <v>46062</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>15</v>
@@ -946,6 +956,7 @@
       <c r="D7" s="9"/>
       <c r="E7" s="4">
         <f>E6+7</f>
+        <v>46426</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>16</v>
@@ -956,6 +967,7 @@
     <row r="8" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f>A7+7</f>
+        <v>46069</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>17</v>
@@ -966,6 +978,7 @@
       </c>
       <c r="E8" s="4">
         <f>E7+7</f>
+        <v>46433</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>19</v>
@@ -978,6 +991,7 @@
     <row r="9" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <f>A8+7</f>
+        <v>46076</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>21</v>
@@ -986,6 +1000,7 @@
       <c r="D9" s="9"/>
       <c r="E9" s="4">
         <f>E8+7</f>
+        <v>46440</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>22</v>
@@ -996,6 +1011,7 @@
     <row r="10" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <f>A9+7</f>
+        <v>46083</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>23</v>
@@ -1004,6 +1020,7 @@
       <c r="D10" s="9"/>
       <c r="E10" s="4">
         <f>E9+7</f>
+        <v>46447</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>24</v>
@@ -1016,6 +1033,7 @@
     <row r="11" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <f>A10+7</f>
+        <v>46090</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>26</v>
@@ -1024,6 +1042,7 @@
       <c r="D11" s="9"/>
       <c r="E11" s="4">
         <f>E10+7</f>
+        <v>46454</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="10" t="s">
@@ -1034,6 +1053,7 @@
     <row r="12" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <f>A11+7</f>
+        <v>46097</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>28</v>
@@ -1042,6 +1062,7 @@
       <c r="D12" s="9"/>
       <c r="E12" s="4">
         <f>E11+7</f>
+        <v>46461</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="10" t="s">
@@ -1052,6 +1073,7 @@
     <row r="13" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <f>A12+7</f>
+        <v>46104</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>30</v>
@@ -1060,6 +1082,7 @@
       <c r="D13" s="9"/>
       <c r="E13" s="4">
         <f>E12+7</f>
+        <v>46468</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="10" t="s">
@@ -1072,12 +1095,14 @@
     <row r="14" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <f>A13+7</f>
+        <v>46111</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="9"/>
       <c r="E14" s="4">
         <f>E13+7</f>
+        <v>46475</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="10" t="s">
@@ -1088,6 +1113,7 @@
     <row r="15" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <f>A14+7</f>
+        <v>46118</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>34</v>
@@ -1096,6 +1122,7 @@
       <c r="D15" s="9"/>
       <c r="E15" s="4">
         <f>E14+7</f>
+        <v>46482</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="10" t="s">
@@ -1106,6 +1133,7 @@
     <row r="16" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <f>A15+7</f>
+        <v>46125</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>36</v>
@@ -1114,6 +1142,7 @@
       <c r="D16" s="9"/>
       <c r="E16" s="4">
         <f>E15+7</f>
+        <v>46489</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="10" t="s">
@@ -1124,6 +1153,7 @@
     <row r="17" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <f>A16+7</f>
+        <v>46132</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>38</v>
@@ -1132,6 +1162,7 @@
       <c r="D17" s="9"/>
       <c r="E17" s="4">
         <f>E16+7</f>
+        <v>46496</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="10" t="s">
@@ -1142,6 +1173,7 @@
     <row r="18" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <f>A17+7</f>
+        <v>46139</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>40</v>
@@ -1150,6 +1182,7 @@
       <c r="D18" s="9"/>
       <c r="E18" s="4">
         <f>E17+7</f>
+        <v>46503</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
@@ -1158,6 +1191,7 @@
     <row r="19" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <f>A18+7</f>
+        <v>46146</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>41</v>
@@ -1166,6 +1200,7 @@
       <c r="D19" s="9"/>
       <c r="E19" s="4">
         <f>E18+7</f>
+        <v>46510</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
@@ -1174,6 +1209,7 @@
     <row r="20" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <f>A19+7</f>
+        <v>46153</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>42</v>
@@ -1182,6 +1218,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="4">
         <f>E19+7</f>
+        <v>46517</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
@@ -1190,6 +1227,7 @@
     <row r="21" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <f>A20+7</f>
+        <v>46160</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>43</v>
@@ -1198,6 +1236,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="4">
         <f>E20+7</f>
+        <v>46524</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
@@ -1206,6 +1245,7 @@
     <row r="22" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <f>A21+7</f>
+        <v>46167</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>44</v>
@@ -1216,6 +1256,7 @@
       </c>
       <c r="E22" s="4">
         <f>E21+7</f>
+        <v>46531</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
@@ -1224,6 +1265,7 @@
     <row r="23" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <f>A22+7</f>
+        <v>46174</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>46</v>
@@ -1232,6 +1274,7 @@
       <c r="D23" s="9"/>
       <c r="E23" s="4">
         <f>E22+7</f>
+        <v>46538</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
@@ -1240,6 +1283,7 @@
     <row r="24" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <f>A23+7</f>
+        <v>46181</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>47</v>
@@ -1248,6 +1292,7 @@
       <c r="D24" s="9"/>
       <c r="E24" s="4">
         <f>E23+7</f>
+        <v>46545</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
@@ -1256,6 +1301,7 @@
     <row r="25" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <f>A24+7</f>
+        <v>46188</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>48</v>
@@ -1266,6 +1312,7 @@
       </c>
       <c r="E25" s="4">
         <f>E24+7</f>
+        <v>46552</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
@@ -1274,6 +1321,7 @@
     <row r="26" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <f>A25+7</f>
+        <v>46195</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>50</v>
@@ -1282,6 +1330,7 @@
       <c r="D26" s="9"/>
       <c r="E26" s="4">
         <f>E25+7</f>
+        <v>46559</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
@@ -1290,6 +1339,7 @@
     <row r="27" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <f>A26+7</f>
+        <v>46202</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>51</v>
@@ -1300,6 +1350,7 @@
       </c>
       <c r="E27" s="4">
         <f>E26+7</f>
+        <v>46566</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
@@ -1308,6 +1359,7 @@
     <row r="28" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <f>A27+7</f>
+        <v>46209</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>53</v>
@@ -1316,6 +1368,7 @@
       <c r="D28" s="9"/>
       <c r="E28" s="4">
         <f>E27+7</f>
+        <v>46573</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
@@ -1324,6 +1377,7 @@
     <row r="29" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <f>A28+7</f>
+        <v>46216</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>54</v>
@@ -1332,6 +1386,7 @@
       <c r="D29" s="9"/>
       <c r="E29" s="4">
         <f>E28+7</f>
+        <v>46580</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
@@ -1340,6 +1395,7 @@
     <row r="30" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <f>A29+7</f>
+        <v>46223</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>55</v>
@@ -1348,6 +1404,7 @@
       <c r="D30" s="9"/>
       <c r="E30" s="4">
         <f>E29+7</f>
+        <v>46587</v>
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
@@ -1356,6 +1413,7 @@
     <row r="31" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <f>A30+7</f>
+        <v>46230</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>56</v>
@@ -1364,6 +1422,7 @@
       <c r="D31" s="9"/>
       <c r="E31" s="4">
         <f>E30+7</f>
+        <v>46594</v>
       </c>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
@@ -1372,6 +1431,7 @@
     <row r="32" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <f>A31+7</f>
+        <v>46237</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>57</v>
@@ -1380,6 +1440,7 @@
       <c r="D32" s="9"/>
       <c r="E32" s="4">
         <f>E31+7</f>
+        <v>46601</v>
       </c>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
@@ -1388,6 +1449,7 @@
     <row r="33" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <f>A32+7</f>
+        <v>46244</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>58</v>
@@ -1396,6 +1458,7 @@
       <c r="D33" s="9"/>
       <c r="E33" s="4">
         <f>E32+7</f>
+        <v>46608</v>
       </c>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
@@ -1404,6 +1467,7 @@
     <row r="34" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <f>A33+7</f>
+        <v>46251</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>59</v>
@@ -1412,6 +1476,7 @@
       <c r="D34" s="9"/>
       <c r="E34" s="4">
         <f>E33+7</f>
+        <v>46615</v>
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
@@ -1420,6 +1485,7 @@
     <row r="35" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <f>A34+7</f>
+        <v>46258</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>60</v>
@@ -1428,6 +1494,7 @@
       <c r="D35" s="15"/>
       <c r="E35" s="4">
         <f>E34+7</f>
+        <v>46622</v>
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
@@ -1436,6 +1503,7 @@
     <row r="36" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <f>A35+7</f>
+        <v>46265</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>60</v>
@@ -1444,6 +1512,7 @@
       <c r="D36" s="15"/>
       <c r="E36" s="4">
         <f>E35+7</f>
+        <v>46629</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
@@ -1452,6 +1521,7 @@
     <row r="37" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <f>A36+7</f>
+        <v>46272</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>61</v>
@@ -1462,6 +1532,7 @@
       </c>
       <c r="E37" s="4">
         <f>E36+7</f>
+        <v>46636</v>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
@@ -1470,6 +1541,7 @@
     <row r="38" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <f>A37+7</f>
+        <v>46279</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>63</v>
@@ -1478,6 +1550,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="4">
         <f>E37+7</f>
+        <v>46643</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
@@ -1486,6 +1559,7 @@
     <row r="39" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <f>A38+7</f>
+        <v>46286</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>64</v>
@@ -1494,6 +1568,7 @@
       <c r="D39" s="9"/>
       <c r="E39" s="4">
         <f>E38+7</f>
+        <v>46650</v>
       </c>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
@@ -1502,6 +1577,7 @@
     <row r="40" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <f>A39+7</f>
+        <v>46293</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>65</v>
@@ -1510,6 +1586,7 @@
       <c r="D40" s="9"/>
       <c r="E40" s="4">
         <f>E39+7</f>
+        <v>46657</v>
       </c>
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
@@ -1518,6 +1595,7 @@
     <row r="41" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <f>A40+7</f>
+        <v>46300</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>66</v>
@@ -1526,6 +1604,7 @@
       <c r="D41" s="9"/>
       <c r="E41" s="4">
         <f>E40+7</f>
+        <v>46664</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
@@ -1534,6 +1613,7 @@
     <row r="42" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <f>A41+7</f>
+        <v>46307</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>67</v>
@@ -1542,6 +1622,7 @@
       <c r="D42" s="9"/>
       <c r="E42" s="4">
         <f>E41+7</f>
+        <v>46671</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
@@ -1550,6 +1631,7 @@
     <row r="43" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <f>A42+7</f>
+        <v>46314</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>68</v>
@@ -1558,6 +1640,7 @@
       <c r="D43" s="9"/>
       <c r="E43" s="4">
         <f>E42+7</f>
+        <v>46678</v>
       </c>
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
@@ -1566,6 +1649,7 @@
     <row r="44" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <f>A43+7</f>
+        <v>46321</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>69</v>
@@ -1574,6 +1658,7 @@
       <c r="D44" s="9"/>
       <c r="E44" s="4">
         <f>E43+7</f>
+        <v>46685</v>
       </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
@@ -1582,6 +1667,7 @@
     <row r="45" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <f>A44+7</f>
+        <v>46328</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>70</v>
@@ -1594,6 +1680,7 @@
       </c>
       <c r="E45" s="4">
         <f>E44+7</f>
+        <v>46692</v>
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
@@ -1602,6 +1689,7 @@
     <row r="46" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <f>A45+7</f>
+        <v>46335</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="7" t="s">
@@ -1610,6 +1698,7 @@
       <c r="D46" s="9"/>
       <c r="E46" s="4">
         <f>E45+7</f>
+        <v>46699</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
@@ -1618,6 +1707,7 @@
     <row r="47" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <f>A46+7</f>
+        <v>46342</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="7" t="s">
@@ -1626,6 +1716,7 @@
       <c r="D47" s="9"/>
       <c r="E47" s="4">
         <f>E46+7</f>
+        <v>46706</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
@@ -1634,6 +1725,7 @@
     <row r="48" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <f>A47+7</f>
+        <v>46349</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="7" t="s">
@@ -1644,6 +1736,7 @@
       </c>
       <c r="E48" s="4">
         <f>E47+7</f>
+        <v>46713</v>
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
@@ -1652,6 +1745,7 @@
     <row r="49" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <f>A48+7</f>
+        <v>46356</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="7" t="s">
@@ -1660,6 +1754,7 @@
       <c r="D49" s="9"/>
       <c r="E49" s="4">
         <f>E48+7</f>
+        <v>46720</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
@@ -1668,6 +1763,7 @@
     <row r="50" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <f>A49+7</f>
+        <v>46363</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="7" t="s">
@@ -1676,6 +1772,7 @@
       <c r="D50" s="9"/>
       <c r="E50" s="4">
         <f>E49+7</f>
+        <v>46727</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
@@ -1684,6 +1781,7 @@
     <row r="51" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <f>A50+7</f>
+        <v>46370</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="7" t="s">
@@ -1692,6 +1790,7 @@
       <c r="D51" s="9"/>
       <c r="E51" s="4">
         <f>E50+7</f>
+        <v>46734</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
@@ -1700,6 +1799,7 @@
     <row r="52" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <f>A51+7</f>
+        <v>46377</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>60</v>
@@ -1708,6 +1808,7 @@
       <c r="D52" s="15"/>
       <c r="E52" s="4">
         <f>E51+7</f>
+        <v>46741</v>
       </c>
       <c r="F52" s="15" t="s">
         <v>60</v>
@@ -1718,6 +1819,7 @@
     <row r="53" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="16">
         <f>A52+7</f>
+        <v>46384</v>
       </c>
       <c r="B53" s="17" t="s">
         <v>60</v>
@@ -1726,6 +1828,7 @@
       <c r="D53" s="17"/>
       <c r="E53" s="16">
         <f>E52+7</f>
+        <v>46748</v>
       </c>
       <c r="F53" s="17" t="s">
         <v>60</v>
